--- a/vocabulary.xlsx
+++ b/vocabulary.xlsx
@@ -21,7 +21,7 @@
     <t>ConceptScheme URI</t>
   </si>
   <si>
-    <t>http://purl.ontoforge.org/wedo/reilatax</t>
+    <t>http://purl.ontoforge.org/wedo/reilatax/</t>
   </si>
   <si>
     <t>PREFIX</t>
@@ -2114,7 +2114,7 @@
     <font>
       <u/>
       <sz val="12.0"/>
-      <color rgb="FF000000"/>
+      <color rgb="FF0000FF"/>
       <name val="Cambria"/>
     </font>
     <font>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="C2" s="5" t="str">
         <f>B1</f>
-        <v>http://purl.ontoforge.org/wedo/reilatax</v>
+        <v>http://purl.ontoforge.org/wedo/reilatax/</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>

--- a/vocabulary.xlsx
+++ b/vocabulary.xlsx
@@ -21,7 +21,7 @@
     <t>ConceptScheme URI</t>
   </si>
   <si>
-    <t>http://purl.ontoforge.org/wedo/reilatax/</t>
+    <t>http://purl.ontoforge.org/wedo/reliatax/</t>
   </si>
   <si>
     <t>PREFIX</t>
@@ -2114,7 +2114,7 @@
     <font>
       <u/>
       <sz val="12.0"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF0563C1"/>
       <name val="Cambria"/>
     </font>
     <font>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="C2" s="5" t="str">
         <f>B1</f>
-        <v>http://purl.ontoforge.org/wedo/reilatax/</v>
+        <v>http://purl.ontoforge.org/wedo/reliatax/</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
